--- a/public/templates/FA_sample_template.xlsx
+++ b/public/templates/FA_sample_template.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+  <si>
+    <t>Asset Code</t>
+  </si>
+  <si>
+    <t>Asset Name</t>
   </si>
   <si>
     <t>Location</t>
@@ -52,9 +52,6 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>Sub Total</t>
-  </si>
-  <si>
     <t>Tax</t>
   </si>
   <si>
@@ -94,13 +91,10 @@
     <t>Present asset value</t>
   </si>
   <si>
-    <t>Supplier company name</t>
+    <t>Supplier display name</t>
   </si>
   <si>
     <t>Transaction currency(INR,USD)</t>
-  </si>
-  <si>
-    <t>Pre-tax amount</t>
   </si>
   <si>
     <t>Tax amount</t>
@@ -162,9 +156,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,12 +180,23 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -207,6 +211,14 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -218,18 +230,27 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,168 +465,149 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.0"/>
-    <col customWidth="1" min="3" max="3" width="14.88"/>
     <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="5" max="5" width="14.88"/>
-    <col customWidth="1" min="6" max="6" width="19.88"/>
-    <col customWidth="1" min="7" max="7" width="34.13"/>
-    <col customWidth="1" min="8" max="8" width="13.13"/>
-    <col customWidth="1" min="9" max="9" width="38.13"/>
-    <col customWidth="1" min="11" max="11" width="15.25"/>
     <col customWidth="1" min="12" max="12" width="19.0"/>
-    <col customWidth="1" min="13" max="13" width="23.75"/>
-    <col customWidth="1" min="16" max="16" width="20.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1000.0</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1000.0</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="3">
-        <v>900.0</v>
-      </c>
-      <c r="O3" s="3">
+      <c r="N3" s="6">
         <v>100.0</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>38</v>
+      <c r="O3" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/FA_sample_template.xlsx
+++ b/public/templates/FA_sample_template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
   <si>
     <t>Asset Code</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>Tax</t>
-  </si>
-  <si>
     <t>Book Date</t>
   </si>
   <si>
@@ -97,13 +94,10 @@
     <t>Transaction currency(INR,USD)</t>
   </si>
   <si>
-    <t>Tax amount</t>
-  </si>
-  <si>
     <t>entry date (DD-MM-YYYY)</t>
   </si>
   <si>
-    <t>LAPTOP01</t>
+    <t>MONITOR147</t>
   </si>
   <si>
     <t>Laptop</t>
@@ -130,14 +124,23 @@
     <t>Staqo</t>
   </si>
   <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>LAPTOP059I</t>
+  </si>
+  <si>
     <t>INR</t>
+  </si>
+  <si>
+    <t>LAPTOP07K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -157,6 +160,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -230,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -251,6 +258,18 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,84 +531,78 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="J3" s="6">
         <v>1.0</v>
@@ -598,17 +611,112 @@
         <v>1000.0</v>
       </c>
       <c r="L3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1000.0</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="6">
-        <v>100.0</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="N4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1000.0</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>36</v>
       </c>
+      <c r="M5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/public/templates/FA_sample_template.xlsx
+++ b/public/templates/FA_sample_template.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+  <si>
+    <t>Series</t>
+  </si>
   <si>
     <t>Asset Code</t>
   </si>
@@ -55,6 +58,9 @@
     <t>Book Date</t>
   </si>
   <si>
+    <t>Book Series (Should same in all rows)</t>
+  </si>
+  <si>
     <t>Asset Unique code (in CAPS)</t>
   </si>
   <si>
@@ -97,10 +103,13 @@
     <t>entry date (DD-MM-YYYY)</t>
   </si>
   <si>
-    <t>MONITOR147</t>
-  </si>
-  <si>
-    <t>Laptop</t>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>M01</t>
+  </si>
+  <si>
+    <t>Monitor</t>
   </si>
   <si>
     <t>India</t>
@@ -125,22 +134,13 @@
   </si>
   <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>LAPTOP059I</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t>LAPTOP07K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -160,10 +160,6 @@
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -237,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -258,18 +254,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,15 +468,21 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="12" max="12" width="19.0"/>
+    <col customWidth="1" min="1" max="1" width="29.25"/>
+    <col customWidth="1" min="2" max="2" width="22.0"/>
+    <col customWidth="1" min="5" max="5" width="17.0"/>
+    <col customWidth="1" min="8" max="8" width="29.63"/>
+    <col customWidth="1" min="9" max="9" width="13.13"/>
+    <col customWidth="1" min="10" max="10" width="38.0"/>
+    <col customWidth="1" min="13" max="13" width="19.0"/>
+    <col customWidth="1" min="15" max="15" width="20.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -530,193 +520,121 @@
       </c>
       <c r="N1" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="6">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="6">
         <v>10.0</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="6">
         <v>1.0</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="6">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="M3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>1000.0</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="K5" s="10">
-        <v>1000.0</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
